--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.02857142857142857</v>
+        <v>0.01418439716312057</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.04225352112676056</v>
+        <v>0.02112676056338028</v>
       </c>
       <c r="D2">
-        <v>0.9714285714285714</v>
+        <v>0.9858156028368794</v>
       </c>
       <c r="E2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
